--- a/INDEX/INDEX_261028.xlsx
+++ b/INDEX/INDEX_261028.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L314"/>
+  <dimension ref="A1:L320"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -93,7 +93,7 @@
         </is>
       </c>
       <c r="I2">
-        <v>92628741335.0</v>
+        <v>92628741335</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -141,7 +141,7 @@
         </is>
       </c>
       <c r="I3">
-        <v>92354022673.0</v>
+        <v>92354022673</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -189,7 +189,7 @@
         </is>
       </c>
       <c r="I4">
-        <v>93028821592.0</v>
+        <v>93028821592</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -237,7 +237,7 @@
         </is>
       </c>
       <c r="I5">
-        <v>92619428653.0</v>
+        <v>92619428653</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -285,7 +285,7 @@
         </is>
       </c>
       <c r="I6">
-        <v>91818649201.0</v>
+        <v>91818649201</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -333,7 +333,7 @@
         </is>
       </c>
       <c r="I7">
-        <v>92402069775.0</v>
+        <v>92402069775</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -381,7 +381,7 @@
         </is>
       </c>
       <c r="I8">
-        <v>94173786237.0</v>
+        <v>94173786237</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -429,7 +429,7 @@
         </is>
       </c>
       <c r="I9">
-        <v>94322154614.0</v>
+        <v>94322154614</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="I10">
-        <v>94322154615.0</v>
+        <v>94322154615</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="I11">
-        <v>92416772464.0</v>
+        <v>92416772464</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="I12">
-        <v>92572234235.0</v>
+        <v>92572234235</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="I13">
-        <v>89258830163.0</v>
+        <v>89258830163</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="I14">
-        <v>91509466268.0</v>
+        <v>91509466268</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="I15">
-        <v>92237187289.0</v>
+        <v>92237187289</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="I16">
-        <v>93427215300.0</v>
+        <v>93427215300</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="I17">
-        <v>92408614837.0</v>
+        <v>92408614837</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="I18">
-        <v>89643498260.0</v>
+        <v>89643498260</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="I19">
-        <v>75361068851.0</v>
+        <v>75361068851</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="I20">
-        <v>70920207939.0</v>
+        <v>70920207939</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="I21">
-        <v>75666972425.0</v>
+        <v>75666972425</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="I22">
-        <v>88408576099.0</v>
+        <v>88408576099</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="I23">
-        <v>92321692179.0</v>
+        <v>92321692179</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="I24">
-        <v>86681495122.0</v>
+        <v>86681495122</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="I25">
-        <v>92276550466.0</v>
+        <v>92276550466</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="I26">
-        <v>93300885107.0</v>
+        <v>93300885107</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="I27">
-        <v>92134713781.0</v>
+        <v>92134713781</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="I28">
-        <v>90767600957.0</v>
+        <v>90767600957</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="I29">
-        <v>91496494653.0</v>
+        <v>91496494653</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="I30">
-        <v>91289410151.0</v>
+        <v>91289410151</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="I31">
-        <v>91289410144.0</v>
+        <v>91289410144</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="I32">
-        <v>92188460455.0</v>
+        <v>92188460455</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="I33">
-        <v>92188460517.0</v>
+        <v>92188460517</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="I34">
-        <v>92188460511.0</v>
+        <v>92188460511</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="I35">
-        <v>92188460488.0</v>
+        <v>92188460488</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="I36">
-        <v>92188460544.0</v>
+        <v>92188460544</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="I37">
-        <v>92188460478.0</v>
+        <v>92188460478</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="I38">
-        <v>92188460483.0</v>
+        <v>92188460483</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="I39">
-        <v>92188460512.0</v>
+        <v>92188460512</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="I40">
-        <v>92187280532.0</v>
+        <v>92187280532</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="I41">
-        <v>92135792131.0</v>
+        <v>92135792131</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="I42">
-        <v>92187280511.0</v>
+        <v>92187280511</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="I43">
-        <v>92187280489.0</v>
+        <v>92187280489</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="I44">
-        <v>92187280473.0</v>
+        <v>92187280473</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="I45">
-        <v>92187280472.0</v>
+        <v>92187280472</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         </is>
       </c>
       <c r="I46">
-        <v>92187280503.0</v>
+        <v>92187280503</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="I47">
-        <v>92187280476.0</v>
+        <v>92187280476</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="I48">
-        <v>92187280481.0</v>
+        <v>92187280481</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="I49">
-        <v>87086632169.0</v>
+        <v>87086632169</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="I50">
-        <v>86483617377.0</v>
+        <v>86483617377</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="I51">
-        <v>86483617305.0</v>
+        <v>86483617305</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="I52">
-        <v>93029290513.0</v>
+        <v>93029290513</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         </is>
       </c>
       <c r="I53">
-        <v>94532700429.0</v>
+        <v>94532700429</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="I54">
-        <v>94532700425.0</v>
+        <v>94532700425</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="I55">
-        <v>94532700431.0</v>
+        <v>94532700431</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="I56">
-        <v>94532700424.0</v>
+        <v>94532700424</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="I57">
-        <v>92416772491.0</v>
+        <v>92416772491</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="I58">
-        <v>89452185912.0</v>
+        <v>89452185912</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="I59">
-        <v>92416772442.0</v>
+        <v>92416772442</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="I60">
-        <v>92416772453.0</v>
+        <v>92416772453</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="I61">
-        <v>86483617562.0</v>
+        <v>86483617562</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="I62">
-        <v>86483777222.0</v>
+        <v>86483777222</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         </is>
       </c>
       <c r="I63">
-        <v>92188592406.0</v>
+        <v>92188592406</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         </is>
       </c>
       <c r="I64">
-        <v>92600607651.0</v>
+        <v>92600607651</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3112,7 +3112,7 @@
         </is>
       </c>
       <c r="I65">
-        <v>92140841716.0</v>
+        <v>92140841716</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="I66">
-        <v>86681495158.0</v>
+        <v>86681495158</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="I67">
-        <v>86003745230.0</v>
+        <v>86003745230</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="I68">
-        <v>91091341360.0</v>
+        <v>91091341360</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="I69">
-        <v>93276664024.0</v>
+        <v>93276664024</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="I70">
-        <v>87626555999.0</v>
+        <v>87626555999</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="I71">
-        <v>92382948154.0</v>
+        <v>92382948154</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="I72">
-        <v>92866056870.0</v>
+        <v>92866056870</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="I73">
-        <v>91002647588.0</v>
+        <v>91002647588</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="I74">
-        <v>92416772523.0</v>
+        <v>92416772523</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="I75">
-        <v>73361761013.0</v>
+        <v>73361761013</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="I76">
-        <v>86043345875.0</v>
+        <v>86043345875</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="I77">
-        <v>91341158791.0</v>
+        <v>91341158791</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="I78">
-        <v>92047389310.0</v>
+        <v>92047389310</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="I79">
-        <v>92416772534.0</v>
+        <v>92416772534</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="I80">
-        <v>82489945582.0</v>
+        <v>82489945582</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="I81">
-        <v>83542939613.0</v>
+        <v>83542939613</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="I82">
-        <v>86043345833.0</v>
+        <v>86043345833</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="I83">
-        <v>70546628743.0</v>
+        <v>70546628743</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         </is>
       </c>
       <c r="I84">
-        <v>92090282778.0</v>
+        <v>92090282778</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I85">
-        <v>92095536885.0</v>
+        <v>92095536885</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="I86">
-        <v>92090282782.0</v>
+        <v>92090282782</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="I87">
-        <v>92045952117.0</v>
+        <v>92045952117</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="I88">
-        <v>92095536887.0</v>
+        <v>92095536887</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         </is>
       </c>
       <c r="I89">
-        <v>92416772479.0</v>
+        <v>92416772479</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="I90">
-        <v>90823426909.0</v>
+        <v>90823426909</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         </is>
       </c>
       <c r="I91">
-        <v>88615962093.0</v>
+        <v>88615962093</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="I92">
-        <v>90784376462.0</v>
+        <v>90784376462</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="I93">
-        <v>90823426912.0</v>
+        <v>90823426912</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="I94">
-        <v>93061378910.0</v>
+        <v>93061378910</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="I95">
-        <v>90784376603.0</v>
+        <v>90784376603</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         </is>
       </c>
       <c r="I96">
-        <v>93061378922.0</v>
+        <v>93061378922</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="I97">
-        <v>93061378883.0</v>
+        <v>93061378883</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         </is>
       </c>
       <c r="I98">
-        <v>91916693866.0</v>
+        <v>91916693866</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="I99">
-        <v>81265075428.0</v>
+        <v>81265075428</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="I100">
-        <v>91289410009.0</v>
+        <v>91289410009</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="I101">
-        <v>93061378895.0</v>
+        <v>93061378895</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         </is>
       </c>
       <c r="I102">
-        <v>91916693871.0</v>
+        <v>91916693871</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="I103">
-        <v>92354022674.0</v>
+        <v>92354022674</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="I104">
-        <v>92740203480.0</v>
+        <v>92740203480</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="I105">
-        <v>87086632286.0</v>
+        <v>87086632286</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         </is>
       </c>
       <c r="I106">
-        <v>92866178692.0</v>
+        <v>92866178692</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="I107">
-        <v>90891197855.0</v>
+        <v>90891197855</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="I108">
-        <v>92096344611.0</v>
+        <v>92096344611</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="I109">
-        <v>93717583055.0</v>
+        <v>93717583055</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="I110">
-        <v>93717583054.0</v>
+        <v>93717583054</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="I111">
-        <v>93679801098.0</v>
+        <v>93679801098</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         </is>
       </c>
       <c r="I112">
-        <v>92188460605.0</v>
+        <v>92188460605</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="I113">
-        <v>92378167476.0</v>
+        <v>92378167476</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="I114">
-        <v>92195376695.0</v>
+        <v>92195376695</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="I115">
-        <v>92869908606.0</v>
+        <v>92869908606</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="I116">
-        <v>92195376640.0</v>
+        <v>92195376640</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="I117">
-        <v>92195376712.0</v>
+        <v>92195376712</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="I118">
-        <v>92194350851.0</v>
+        <v>92194350851</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="I119">
-        <v>91492117679.0</v>
+        <v>91492117679</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="I120">
-        <v>93341310192.0</v>
+        <v>93341310192</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="I121">
-        <v>93553482831.0</v>
+        <v>93553482831</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="I122">
-        <v>92416772429.0</v>
+        <v>92416772429</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="I123">
-        <v>92740203483.0</v>
+        <v>92740203483</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="I124">
-        <v>92866178717.0</v>
+        <v>92866178717</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="I125">
-        <v>94225134070.0</v>
+        <v>94225134070</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="I126">
-        <v>93953419576.0</v>
+        <v>93953419576</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I127">
-        <v>93679801099.0</v>
+        <v>93679801099</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="I128">
-        <v>93679801097.0</v>
+        <v>93679801097</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="I129">
-        <v>93679801096.0</v>
+        <v>93679801096</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="I130">
-        <v>93553482829.0</v>
+        <v>93553482829</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="I131">
-        <v>93448331269.0</v>
+        <v>93448331269</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         </is>
       </c>
       <c r="I132">
-        <v>93448331267.0</v>
+        <v>93448331267</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         </is>
       </c>
       <c r="I133">
-        <v>93341310193.0</v>
+        <v>93341310193</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="I134">
-        <v>92866178674.0</v>
+        <v>92866178674</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="I135">
-        <v>92866178655.0</v>
+        <v>92866178655</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="I136">
-        <v>92837402533.0</v>
+        <v>92837402533</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="I137">
-        <v>92740203475.0</v>
+        <v>92740203475</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="I138">
-        <v>92740203472.0</v>
+        <v>92740203472</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         </is>
       </c>
       <c r="I139">
-        <v>92740203467.0</v>
+        <v>92740203467</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="I140">
-        <v>92740203464.0</v>
+        <v>92740203464</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="I141">
-        <v>92416772415.0</v>
+        <v>92416772415</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="I142">
-        <v>92382915190.0</v>
+        <v>92382915190</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="I143">
-        <v>92262696801.0</v>
+        <v>92262696801</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="I144">
-        <v>92194350868.0</v>
+        <v>92194350868</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="I145">
-        <v>92096344612.0</v>
+        <v>92096344612</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I146">
-        <v>89096431255.0</v>
+        <v>89096431255</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="I147">
-        <v>89096431238.0</v>
+        <v>89096431238</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="I148">
-        <v>88849682621.0</v>
+        <v>88849682621</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="I149">
-        <v>86706653373.0</v>
+        <v>86706653373</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -6932,7 +6932,7 @@
         </is>
       </c>
       <c r="I150">
-        <v>86088854738.0</v>
+        <v>86088854738</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="I151">
-        <v>87923490962.0</v>
+        <v>87923490962</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         </is>
       </c>
       <c r="I152">
-        <v>80555002604.0</v>
+        <v>80555002604</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="I153">
-        <v>93276664023.0</v>
+        <v>93276664023</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="I154">
-        <v>89453052279.0</v>
+        <v>89453052279</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I155">
-        <v>89453052279.0</v>
+        <v>89453052279</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         </is>
       </c>
       <c r="I156">
-        <v>89116270343.0</v>
+        <v>89116270343</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="I157">
-        <v>89397125334.0</v>
+        <v>89397125334</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         </is>
       </c>
       <c r="I158">
-        <v>89397125412.0</v>
+        <v>89397125412</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         </is>
       </c>
       <c r="I159">
-        <v>89453052161.0</v>
+        <v>89453052161</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         </is>
       </c>
       <c r="I160">
-        <v>90464772089.0</v>
+        <v>90464772089</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         </is>
       </c>
       <c r="I161">
-        <v>90464772117.0</v>
+        <v>90464772117</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="I162">
-        <v>90464772120.0</v>
+        <v>90464772120</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         </is>
       </c>
       <c r="I163">
-        <v>90464772130.0</v>
+        <v>90464772130</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="I164">
-        <v>89452185962.0</v>
+        <v>89452185962</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="I165">
-        <v>89452185992.0</v>
+        <v>89452185992</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         </is>
       </c>
       <c r="I166">
-        <v>89567311749.0</v>
+        <v>89567311749</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="I167">
-        <v>89567311779.0</v>
+        <v>89567311779</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         </is>
       </c>
       <c r="I168">
-        <v>90228351828.0</v>
+        <v>90228351828</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="I169">
-        <v>92869696081.0</v>
+        <v>92869696081</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="I170">
-        <v>93553482830.0</v>
+        <v>93553482830</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="I171">
-        <v>92194350860.0</v>
+        <v>92194350860</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         </is>
       </c>
       <c r="I172">
-        <v>92195376630.0</v>
+        <v>92195376630</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="I173">
-        <v>93981018091.0</v>
+        <v>93981018091</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="I174">
-        <v>94994914026.0</v>
+        <v>94994914026</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="I175">
-        <v>94985565824.0</v>
+        <v>94985565824</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="I176">
-        <v>94973962377.0</v>
+        <v>94973962377</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="I177">
-        <v>94973962378.0</v>
+        <v>94973962378</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         </is>
       </c>
       <c r="I178">
-        <v>94973962379.0</v>
+        <v>94973962379</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="I179">
-        <v>94973962380.0</v>
+        <v>94973962380</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="I180">
-        <v>94985438752.0</v>
+        <v>94985438752</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="I181">
-        <v>82478477445.0</v>
+        <v>82478477445</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -8468,7 +8468,7 @@
         </is>
       </c>
       <c r="I182">
-        <v>93981018091.0</v>
+        <v>93981018091</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="I183">
-        <v>94973962245.0</v>
+        <v>94973962245</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="I184">
-        <v>94973962246.0</v>
+        <v>94973962246</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="I185">
-        <v>90492974435.0</v>
+        <v>90492974435</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="I186">
-        <v>87638973523.0</v>
+        <v>87638973523</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="I187">
-        <v>95059252568.0</v>
+        <v>95059252568</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="I188">
-        <v>95059252894.0</v>
+        <v>95059252894</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="I189">
-        <v>89252727577.0</v>
+        <v>89252727577</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         </is>
       </c>
       <c r="I190">
-        <v>89252727930.0</v>
+        <v>89252727930</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="I191">
-        <v>91046487100.0</v>
+        <v>91046487100</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="I192">
-        <v>91288438146.0</v>
+        <v>91288438146</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="I193">
-        <v>95059252810.0</v>
+        <v>95059252810</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="I194">
-        <v>95100222939.0</v>
+        <v>95100222939</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="I195">
-        <v>95100223079.0</v>
+        <v>95100223079</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="I196">
-        <v>95100223080.0</v>
+        <v>95100223080</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         </is>
       </c>
       <c r="I197">
-        <v>93276664024.0</v>
+        <v>93276664024</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         </is>
       </c>
       <c r="I198">
-        <v>92045952117.0</v>
+        <v>92045952117</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         </is>
       </c>
       <c r="I199">
-        <v>92047389310.0</v>
+        <v>92047389310</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="I200">
-        <v>70546628743.0</v>
+        <v>70546628743</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="I201">
-        <v>70920207939.0</v>
+        <v>70920207939</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="I202">
-        <v>90891197855.0</v>
+        <v>90891197855</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         </is>
       </c>
       <c r="I203">
-        <v>92096344611.0</v>
+        <v>92096344611</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         </is>
       </c>
       <c r="I204">
-        <v>92090282778.0</v>
+        <v>92090282778</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         </is>
       </c>
       <c r="I205">
-        <v>86681495122.0</v>
+        <v>86681495122</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         </is>
       </c>
       <c r="I206">
-        <v>86706653373.0</v>
+        <v>86706653373</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="I207">
-        <v>86088854738.0</v>
+        <v>86088854738</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         </is>
       </c>
       <c r="I208">
-        <v>92188460517.0</v>
+        <v>92188460517</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="I209">
-        <v>95059252810.0</v>
+        <v>95059252810</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="I210">
-        <v>92188460605.0</v>
+        <v>92188460605</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         </is>
       </c>
       <c r="I211">
-        <v>95059252568.0</v>
+        <v>95059252568</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         </is>
       </c>
       <c r="I212">
-        <v>92135792131.0</v>
+        <v>92135792131</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         </is>
       </c>
       <c r="I213">
-        <v>92187280511.0</v>
+        <v>92187280511</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         </is>
       </c>
       <c r="I214">
-        <v>92188460527.0</v>
+        <v>92188460527</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         </is>
       </c>
       <c r="I215">
-        <v>92188460455.0</v>
+        <v>92188460455</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         </is>
       </c>
       <c r="I216">
-        <v>91492117679.0</v>
+        <v>91492117679</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="I217">
-        <v>89252727577.0</v>
+        <v>89252727577</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="I218">
-        <v>89252727930.0</v>
+        <v>89252727930</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="I219">
-        <v>90492974435.0</v>
+        <v>90492974435</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="I220">
-        <v>70546628743.0</v>
+        <v>70546628743</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         </is>
       </c>
       <c r="I221">
-        <v>90891197855.0</v>
+        <v>90891197855</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="I222">
-        <v>70920207939.0</v>
+        <v>70920207939</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         </is>
       </c>
       <c r="I223">
-        <v>86088854738.0</v>
+        <v>86088854738</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         </is>
       </c>
       <c r="I224">
-        <v>86706653373.0</v>
+        <v>86706653373</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         </is>
       </c>
       <c r="I225">
-        <v>92090282778.0</v>
+        <v>92090282778</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         </is>
       </c>
       <c r="I226">
-        <v>92096344611.0</v>
+        <v>92096344611</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="I227">
-        <v>86681495122.0</v>
+        <v>86681495122</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="I228">
-        <v>95059252894.0</v>
+        <v>95059252894</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="I229">
-        <v>92187280532.0</v>
+        <v>92187280532</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="I230">
-        <v>86043345875.0</v>
+        <v>86043345875</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         </is>
       </c>
       <c r="I231">
-        <v>92282812506.0</v>
+        <v>92282812506</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="I232">
-        <v>86003745230.0</v>
+        <v>86003745230</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         </is>
       </c>
       <c r="I233">
-        <v>91289410009.0</v>
+        <v>91289410009</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -10964,7 +10964,7 @@
         </is>
       </c>
       <c r="I234">
-        <v>86043345833.0</v>
+        <v>86043345833</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         </is>
       </c>
       <c r="I235">
-        <v>93553482830.0</v>
+        <v>93553482830</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="I236">
-        <v>91289410151.0</v>
+        <v>91289410151</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="I237">
-        <v>91289410144.0</v>
+        <v>91289410144</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         </is>
       </c>
       <c r="I238">
-        <v>91496494653.0</v>
+        <v>91496494653</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         </is>
       </c>
       <c r="I239">
-        <v>93553482831.0</v>
+        <v>93553482831</v>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I240">
-        <v>93525943599.0</v>
+        <v>93525943599</v>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         </is>
       </c>
       <c r="I241">
-        <v>93553482829.0</v>
+        <v>93553482829</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         </is>
       </c>
       <c r="I242">
-        <v>89258830163.0</v>
+        <v>89258830163</v>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         </is>
       </c>
       <c r="I243">
-        <v>93028821592.0</v>
+        <v>93028821592</v>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         </is>
       </c>
       <c r="I244">
-        <v>92188592424.0</v>
+        <v>92188592424</v>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         </is>
       </c>
       <c r="I245">
-        <v>93276664024.0</v>
+        <v>93276664024</v>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         </is>
       </c>
       <c r="I246">
-        <v>92045952117.0</v>
+        <v>92045952117</v>
       </c>
       <c r="J246" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         </is>
       </c>
       <c r="I247">
-        <v>92047389310.0</v>
+        <v>92047389310</v>
       </c>
       <c r="J247" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         </is>
       </c>
       <c r="I248">
-        <v>91818649201.0</v>
+        <v>91818649201</v>
       </c>
       <c r="J248" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         </is>
       </c>
       <c r="I249">
-        <v>92354708118.0</v>
+        <v>92354708118</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         </is>
       </c>
       <c r="I250">
-        <v>91514490327.0</v>
+        <v>91514490327</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         </is>
       </c>
       <c r="I251">
-        <v>91586184541.0</v>
+        <v>91586184541</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         </is>
       </c>
       <c r="I252">
-        <v>92402069781.0</v>
+        <v>92402069781</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         </is>
       </c>
       <c r="I253">
-        <v>94872476374.0</v>
+        <v>94872476374</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -11464,7 +11464,7 @@
         </is>
       </c>
       <c r="I254">
-        <v>94872476375.0</v>
+        <v>94872476375</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         </is>
       </c>
       <c r="I255">
-        <v>94994704879.0</v>
+        <v>94994704879</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         </is>
       </c>
       <c r="I256">
-        <v>95378228327.0</v>
+        <v>95378228327</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="I257">
-        <v>95378228328.0</v>
+        <v>95378228328</v>
       </c>
       <c r="J257" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="I258">
-        <v>95378228329.0</v>
+        <v>95378228329</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="I259">
-        <v>95378228337.0</v>
+        <v>95378228337</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="I260">
-        <v>92402069781.0</v>
+        <v>92402069781</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="I261">
-        <v>93953680547.0</v>
+        <v>93953680547</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         </is>
       </c>
       <c r="I262">
-        <v>88838055497.0</v>
+        <v>88838055497</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="I263">
-        <v>95203519492.0</v>
+        <v>95203519492</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="I264">
-        <v>95203519074.0</v>
+        <v>95203519074</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -11739,7 +11739,7 @@
         </is>
       </c>
       <c r="I265">
-        <v>90228351851.0</v>
+        <v>90228351851</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="I266">
-        <v>95203519086.0</v>
+        <v>95203519086</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="I267">
-        <v>95204503935.0</v>
+        <v>95204503935</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -11814,7 +11814,7 @@
         </is>
       </c>
       <c r="I268">
-        <v>88836079516.0</v>
+        <v>88836079516</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="I269">
-        <v>95200141759.0</v>
+        <v>95200141759</v>
       </c>
       <c r="J269" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         </is>
       </c>
       <c r="I270">
-        <v>95204503938.0</v>
+        <v>95204503938</v>
       </c>
       <c r="J270" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         </is>
       </c>
       <c r="I271">
-        <v>95203519077.0</v>
+        <v>95203519077</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="I272">
-        <v>95200141065.0</v>
+        <v>95200141065</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         </is>
       </c>
       <c r="I273">
-        <v>95200141066.0</v>
+        <v>95200141066</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="I274">
-        <v>95204503936.0</v>
+        <v>95204503936</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="I275">
-        <v>95200141067.0</v>
+        <v>95200141067</v>
       </c>
       <c r="J275" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         </is>
       </c>
       <c r="I276">
-        <v>95203519487.0</v>
+        <v>95203519487</v>
       </c>
       <c r="J276" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         </is>
       </c>
       <c r="I277">
-        <v>95200141068.0</v>
+        <v>95200141068</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         </is>
       </c>
       <c r="I278">
-        <v>95200141757.0</v>
+        <v>95200141757</v>
       </c>
       <c r="J278" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="I279">
-        <v>95203519087.0</v>
+        <v>95203519087</v>
       </c>
       <c r="J279" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         </is>
       </c>
       <c r="I280">
-        <v>95203519075.0</v>
+        <v>95203519075</v>
       </c>
       <c r="J280" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="I281">
-        <v>95203519076.0</v>
+        <v>95203519076</v>
       </c>
       <c r="J281" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         </is>
       </c>
       <c r="I282">
-        <v>95203519078.0</v>
+        <v>95203519078</v>
       </c>
       <c r="J282" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         </is>
       </c>
       <c r="I283">
-        <v>95203519085.0</v>
+        <v>95203519085</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         </is>
       </c>
       <c r="I284">
-        <v>95203519488.0</v>
+        <v>95203519488</v>
       </c>
       <c r="J284" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         </is>
       </c>
       <c r="I285">
-        <v>95203519489.0</v>
+        <v>95203519489</v>
       </c>
       <c r="J285" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         </is>
       </c>
       <c r="I286">
-        <v>95203519491.0</v>
+        <v>95203519491</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="I287">
-        <v>95204503029.0</v>
+        <v>95204503029</v>
       </c>
       <c r="J287" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         </is>
       </c>
       <c r="I288">
-        <v>95204503030.0</v>
+        <v>95204503030</v>
       </c>
       <c r="J288" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         </is>
       </c>
       <c r="I289">
-        <v>95204503937.0</v>
+        <v>95204503937</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="I290">
-        <v>95239202894.0</v>
+        <v>95239202894</v>
       </c>
       <c r="J290" t="inlineStr">
         <is>
@@ -12389,7 +12389,7 @@
         </is>
       </c>
       <c r="I291">
-        <v>95239202897.0</v>
+        <v>95239202897</v>
       </c>
       <c r="J291" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         </is>
       </c>
       <c r="I292">
-        <v>95526136463.0</v>
+        <v>95526136463</v>
       </c>
       <c r="J292" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         </is>
       </c>
       <c r="I293">
-        <v>95526136464.0</v>
+        <v>95526136464</v>
       </c>
       <c r="J293" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="I294">
-        <v>95203519080.0</v>
+        <v>95203519080</v>
       </c>
       <c r="J294" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         </is>
       </c>
       <c r="I295">
-        <v>95203519081.0</v>
+        <v>95203519081</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         </is>
       </c>
       <c r="I296">
-        <v>95342623498.0</v>
+        <v>95342623498</v>
       </c>
       <c r="J296" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         </is>
       </c>
       <c r="I297">
-        <v>95342623499.0</v>
+        <v>95342623499</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         </is>
       </c>
       <c r="I298">
-        <v>95182961778.0</v>
+        <v>95182961778</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="I299">
-        <v>90228351805.0</v>
+        <v>90228351805</v>
       </c>
       <c r="J299" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="I300">
-        <v>95203519079.0</v>
+        <v>95203519079</v>
       </c>
       <c r="J300" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         </is>
       </c>
       <c r="I301">
-        <v>95203519082.0</v>
+        <v>95203519082</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="I302">
-        <v>95203519484.0</v>
+        <v>95203519484</v>
       </c>
       <c r="J302" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         </is>
       </c>
       <c r="I303">
-        <v>95203519493.0</v>
+        <v>95203519493</v>
       </c>
       <c r="J303" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         </is>
       </c>
       <c r="I304">
-        <v>95203519485.0</v>
+        <v>95203519485</v>
       </c>
       <c r="J304" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         </is>
       </c>
       <c r="I305">
-        <v>95203519486.0</v>
+        <v>95203519486</v>
       </c>
       <c r="J305" t="inlineStr">
         <is>
@@ -12764,7 +12764,7 @@
         </is>
       </c>
       <c r="I306">
-        <v>95203519496.0</v>
+        <v>95203519496</v>
       </c>
       <c r="J306" t="inlineStr">
         <is>
@@ -12905,6 +12905,126 @@
       <c r="E314" t="inlineStr">
         <is>
           <t xml:space="preserve">의류케어</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="B315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[PA] TV_노출최대화_수동</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>105361610</v>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TV</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[PA] 의류케어_주력모델_매출최적화</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>104788426</v>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의류케어</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의류케어</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="B317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[PA] 청소기_주력모델_수동성과형</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>104968197</v>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청소기</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청소기</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="B318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[PA] 청소기_진공 청소기</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>105101853</v>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청소기</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">청소기</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[PA] 갤럭시 버즈온_매출최적화</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>105408768</v>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">웨어러블</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">갤럭시버즈온</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[PA] 갤럭시 버즈온_수동성과형</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>105408803</v>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">웨어러블</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">갤럭시버즈온</t>
         </is>
       </c>
     </row>
